--- a/src/database/test/test_npi_improperstate.xlsx
+++ b/src/database/test/test_npi_improperstate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Repositories\XpressCredentialling\src\database\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9538746-3029-4E58-A057-735EAE4A8E65}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCD7E9E5-71AB-43D8-B86D-1A73B248B4E7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="38">
   <si>
     <t>NPI-1</t>
   </si>
@@ -33,27 +33,15 @@
     <t>[]</t>
   </si>
   <si>
-    <t>NO</t>
-  </si>
-  <si>
     <t>F</t>
   </si>
   <si>
     <t>A</t>
   </si>
   <si>
-    <t>MD</t>
-  </si>
-  <si>
     <t>YES</t>
   </si>
   <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>Dr.</t>
-  </si>
-  <si>
     <t>--</t>
   </si>
   <si>
@@ -144,109 +132,7 @@
     <t>TASHA</t>
   </si>
   <si>
-    <t>1288975417000</t>
-  </si>
-  <si>
-    <t>1790843464</t>
-  </si>
-  <si>
-    <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '2100 NEBRASKA AVENUE', 'address_2': 'SUITE 111', 'city': 'FT PIERCE', 'state': 'FL', 'postal_code': '349504831', 'telephone_number': '772-465-6979', 'fax_number': '772-465-4288'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '2100 NEBRASKA AVENUE', 'address_2': 'SUITE 111', 'city': 'FT PIERCE', 'state': 'FL', 'postal_code': '349504831', 'telephone_number': '772-465-6979', 'fax_number': '772-465-4288'}]</t>
-  </si>
-  <si>
-    <t>[{'code': '207Q00000X', 'taxonomy_group': '', 'desc': 'Family Medicine', 'state': 'FL', 'license': '058720', 'primary': True}]</t>
-  </si>
-  <si>
-    <t>[{'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': '263965300', 'state': 'FL'}]</t>
-  </si>
-  <si>
-    <t>HUMAYUN</t>
-  </si>
-  <si>
-    <t>SHAREEF</t>
-  </si>
-  <si>
-    <t>MD DO</t>
-  </si>
-  <si>
-    <t>2006-12-05</t>
-  </si>
-  <si>
-    <t>2010-11-05</t>
-  </si>
-  <si>
-    <t>1705611307000</t>
-  </si>
-  <si>
-    <t>1164535241</t>
-  </si>
-  <si>
-    <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '3795 W BOYNTON BEACH BLVD STE D', 'city': 'BOYNTON BEACH', 'state': 'FL', 'postal_code': '334364502', 'telephone_number': '561-736-2001'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '3795 W BOYNTON BEACH BLVD STE D', 'city': 'BOYNTON BEACH', 'state': 'FL', 'postal_code': '334364502', 'telephone_number': '561-736-2001'}]</t>
-  </si>
-  <si>
-    <t>[{'code': '207QG0300X', 'taxonomy_group': '', 'desc': 'Family Medicine, Geriatric Medicine', 'state': 'NJ', 'license': '25MB05524000', 'primary': False}, {'code': '207R00000X', 'taxonomy_group': '', 'desc': 'Internal Medicine', 'state': 'FL', 'license': 'OS8714', 'primary': False}, {'code': '207QA0505X', 'taxonomy_group': '', 'desc': 'Family Medicine, Adult Medicine', 'state': 'NJ', 'license': '25MB05524000', 'primary': True}, {'code': '207Q00000X', 'taxonomy_group': '', 'desc': 'Family Medicine', 'state': 'NJ', 'license': '25MB05524000', 'primary': False}]</t>
-  </si>
-  <si>
-    <t>[{'endpointType': 'DIRECT', 'endpointTypeDescription': 'Direct Messaging Address', 'endpoint': 'docdanewton@conviva.eclinicaldirectplus.com', 'affiliation': 'N', 'use': 'DIRECT', 'useDescription': 'Direct', 'contentTypeDescription': '', 'country_code': 'US', 'country_name': 'United States', 'address_type': 'DOM', 'address_1': '3795 W Boynton Beach Blvd Ste D', 'city': 'Boynton Beach', 'state': 'FL', 'postal_code': '334364502'}, {'endpointType': 'DIRECT', 'endpointTypeDescription': 'Direct Messaging Address', 'endpoint': 'dean.newton@conviva.eclinicaldirectplus.com', 'affiliation': 'N', 'use': 'DIRECT', 'useDescription': 'Direct', 'contentType': 'CSV', 'contentTypeDescription': 'CSV', 'country_code': 'US', 'country_name': 'United States', 'address_type': 'DOM', 'address_1': '3795 W Boynton Beach Blvd Ste D', 'city': 'Boynton Beach', 'state': 'FL', 'postal_code': '334364502'}]</t>
-  </si>
-  <si>
-    <t>DEAN</t>
-  </si>
-  <si>
-    <t>NEWTON</t>
-  </si>
-  <si>
-    <t>DO</t>
-  </si>
-  <si>
-    <t>2006-08-16</t>
-  </si>
-  <si>
-    <t>2024-01-18</t>
-  </si>
-  <si>
-    <t>1713552503000</t>
-  </si>
-  <si>
-    <t>1427039148</t>
-  </si>
-  <si>
-    <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '1061 HARMON AVE', 'city': 'FORT STEWART', 'state': 'GA', 'postal_code': '313145641', 'telephone_number': '912-435-6965'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '1061 HARMON AVE', 'city': 'FORT STEWART', 'state': 'GA', 'postal_code': '313145641', 'telephone_number': '912-435-6965', 'fax_number': '251-266-3361'}]</t>
-  </si>
-  <si>
-    <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '1350 HICKORY ST', 'city': 'MELBOURNE', 'state': 'FL', 'postal_code': '329013224', 'telephone_number': '321-434-1771', 'fax_number': '321-434-1775'}]</t>
-  </si>
-  <si>
-    <t>[{'code': '207Q00000X', 'taxonomy_group': '', 'desc': 'Family Medicine', 'state': 'GA', 'license': '043606', 'primary': True}]</t>
-  </si>
-  <si>
-    <t>[{'code': '01', 'desc': 'Other (non-Medicare)', 'issuer': 'INDIVIDUAL BCBS NUMBER', 'identifier': '32751', 'state': 'FL'}]</t>
-  </si>
-  <si>
-    <t>MARC</t>
-  </si>
-  <si>
-    <t>EUGENE</t>
-  </si>
-  <si>
-    <t>2005-11-09</t>
-  </si>
-  <si>
-    <t>2024-04-19</t>
-  </si>
-  <si>
-    <t>ELIE</t>
-  </si>
-  <si>
     <t>1369260111000</t>
-  </si>
-  <si>
-    <t>1165339454000</t>
-  </si>
-  <si>
-    <t>1155701851000</t>
-  </si>
-  <si>
-    <t>1131564999000</t>
   </si>
   <si>
     <t>created_epoch</t>
@@ -604,93 +490,93 @@
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>75</v>
+        <v>37</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="B2" t="s">
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F2" t="s">
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H2" t="s">
         <v>1</v>
@@ -702,218 +588,38 @@
         <v>1</v>
       </c>
       <c r="K2" t="s">
+        <v>30</v>
+      </c>
+      <c r="L2" t="s">
+        <v>31</v>
+      </c>
+      <c r="N2" t="s">
+        <v>4</v>
+      </c>
+      <c r="O2" t="s">
+        <v>2</v>
+      </c>
+      <c r="P2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>33</v>
+      </c>
+      <c r="R2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S2" t="s">
+        <v>5</v>
+      </c>
+      <c r="T2" t="s">
+        <v>5</v>
+      </c>
+      <c r="V2" t="s">
         <v>34</v>
-      </c>
-      <c r="L2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N2" t="s">
-        <v>6</v>
-      </c>
-      <c r="O2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P2" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>37</v>
-      </c>
-      <c r="R2" t="s">
-        <v>4</v>
-      </c>
-      <c r="S2" t="s">
-        <v>9</v>
-      </c>
-      <c r="T2" t="s">
-        <v>9</v>
-      </c>
-      <c r="V2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D3" t="s">
-        <v>40</v>
-      </c>
-      <c r="E3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F3" t="s">
-        <v>1</v>
-      </c>
-      <c r="G3" t="s">
-        <v>42</v>
-      </c>
-      <c r="H3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I3" t="s">
-        <v>1</v>
-      </c>
-      <c r="J3" t="s">
-        <v>1</v>
-      </c>
-      <c r="K3" t="s">
-        <v>44</v>
-      </c>
-      <c r="L3" t="s">
-        <v>45</v>
-      </c>
-      <c r="M3" t="s">
-        <v>46</v>
-      </c>
-      <c r="N3" t="s">
-        <v>6</v>
-      </c>
-      <c r="O3" t="s">
-        <v>7</v>
-      </c>
-      <c r="P3" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>48</v>
-      </c>
-      <c r="R3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>72</v>
-      </c>
-      <c r="B4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E4" t="s">
-        <v>51</v>
-      </c>
-      <c r="F4" t="s">
-        <v>1</v>
-      </c>
-      <c r="G4" t="s">
-        <v>52</v>
-      </c>
-      <c r="H4" t="s">
-        <v>1</v>
-      </c>
-      <c r="I4" t="s">
-        <v>53</v>
-      </c>
-      <c r="J4" t="s">
-        <v>1</v>
-      </c>
-      <c r="K4" t="s">
-        <v>54</v>
-      </c>
-      <c r="L4" t="s">
-        <v>55</v>
-      </c>
-      <c r="M4" t="s">
-        <v>56</v>
-      </c>
-      <c r="N4" t="s">
-        <v>2</v>
-      </c>
-      <c r="O4" t="s">
-        <v>7</v>
-      </c>
-      <c r="P4" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>58</v>
-      </c>
-      <c r="R4" t="s">
-        <v>4</v>
-      </c>
-      <c r="U4" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B5" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" t="s">
-        <v>59</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E5" t="s">
-        <v>61</v>
-      </c>
-      <c r="F5" t="s">
-        <v>62</v>
-      </c>
-      <c r="G5" t="s">
-        <v>63</v>
-      </c>
-      <c r="H5" t="s">
-        <v>64</v>
-      </c>
-      <c r="I5" t="s">
-        <v>1</v>
-      </c>
-      <c r="J5" t="s">
-        <v>1</v>
-      </c>
-      <c r="K5" t="s">
-        <v>65</v>
-      </c>
-      <c r="L5" t="s">
-        <v>66</v>
-      </c>
-      <c r="M5" t="s">
-        <v>5</v>
-      </c>
-      <c r="N5" t="s">
-        <v>2</v>
-      </c>
-      <c r="O5" t="s">
-        <v>7</v>
-      </c>
-      <c r="P5" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>68</v>
-      </c>
-      <c r="R5" t="s">
-        <v>4</v>
-      </c>
-      <c r="U5" t="s">
-        <v>68</v>
-      </c>
-      <c r="V5" t="s">
-        <v>69</v>
-      </c>
+      <c r="D5" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
